--- a/xls/square_16_quad4_12.xlsx
+++ b/xls/square_16_quad4_12.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>289</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>300</v>
+      </c>
+      <c r="I10">
+        <v>3.299132077052728</v>
+      </c>
+      <c r="J10">
+        <v>0.9174587667284992</v>
+      </c>
+      <c r="K10">
+        <v>1.103690817792263</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>289</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>363</v>
+      </c>
+      <c r="I11">
+        <v>1.6559683706663268</v>
+      </c>
+      <c r="J11">
+        <v>-0.16092374836893653</v>
+      </c>
+      <c r="K11">
+        <v>0.2758813717010047</v>
+      </c>
+    </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>432</v>
       </c>
       <c r="I12">
-        <v>2.970426479974575</v>
+        <v>1.9087181285021502</v>
       </c>
       <c r="J12">
-        <v>-0.09600809931904343</v>
+        <v>-0.7093680188141078</v>
       </c>
       <c r="K12">
-        <v>0.49111715872440415</v>
+        <v>0.09253178281215489</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -517,13 +587,13 @@
         <v>507</v>
       </c>
       <c r="I13">
-        <v>-1.573471564398879</v>
+        <v>-1.2441730274874174</v>
       </c>
       <c r="J13">
-        <v>-1.5789132968994444</v>
+        <v>-1.289624004916609</v>
       </c>
       <c r="K13">
-        <v>-1.2279721383168027</v>
+        <v>-1.2054959061634696</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -552,13 +622,13 @@
         <v>588</v>
       </c>
       <c r="I14">
-        <v>-1.6310029419257202</v>
+        <v>-1.3027887705253949</v>
       </c>
       <c r="J14">
-        <v>-1.656610621894003</v>
+        <v>-1.3472690744992886</v>
       </c>
       <c r="K14">
-        <v>-1.309867884220016</v>
+        <v>-1.2773029214045235</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -587,13 +657,13 @@
         <v>675</v>
       </c>
       <c r="I15">
-        <v>-1.7006532249604824</v>
+        <v>-1.3645767073242498</v>
       </c>
       <c r="J15">
-        <v>-1.722081501629334</v>
+        <v>-1.409813930177527</v>
       </c>
       <c r="K15">
-        <v>-1.179322926184904</v>
+        <v>-1.229591099199325</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -622,13 +692,13 @@
         <v>768</v>
       </c>
       <c r="I16">
-        <v>-1.7796627733461596</v>
+        <v>-1.439711387159956</v>
       </c>
       <c r="J16">
-        <v>-1.7736302617759239</v>
+        <v>-1.4942207953692102</v>
       </c>
       <c r="K16">
-        <v>-0.9162289099502956</v>
+        <v>-1.0312339161982063</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -657,13 +727,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-1.8244175644319591</v>
+        <v>-1.487045117399235</v>
       </c>
       <c r="J17">
-        <v>-1.803587964852425</v>
+        <v>-1.5290793480437834</v>
       </c>
       <c r="K17">
-        <v>2.192193211122345</v>
+        <v>0.9034764747069217</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -692,13 +762,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-1.114186390338154</v>
+        <v>-0.7206922696497053</v>
       </c>
       <c r="J18">
-        <v>-1.0289457763198968</v>
+        <v>-0.7608560363242794</v>
       </c>
       <c r="K18">
-        <v>3.5947895257911804</v>
+        <v>4.021008790221218</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-0.25691283540299925</v>
+        <v>-0.005529945341222665</v>
       </c>
       <c r="J19">
-        <v>-0.24241464207868163</v>
+        <v>-0.00680167015305243</v>
       </c>
       <c r="K19">
-        <v>3.9480849886964835</v>
+        <v>4.327103887550831</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-0.08917073106976835</v>
+        <v>-0.0024066871164518575</v>
       </c>
       <c r="J20">
-        <v>-0.08911775562827337</v>
+        <v>-0.002543466360629856</v>
       </c>
       <c r="K20">
-        <v>3.8074759404467606</v>
+        <v>4.08890739222119</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -797,13 +867,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-0.016460771625779483</v>
+        <v>-0.00014654736970848276</v>
       </c>
       <c r="J21">
-        <v>-0.013757497936645213</v>
+        <v>-0.00013291554942996127</v>
       </c>
       <c r="K21">
-        <v>3.4757706256856595</v>
+        <v>3.429904827745944</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -832,13 +902,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-0.0335991726161315</v>
+        <v>-0.00024807708194689244</v>
       </c>
       <c r="J22">
-        <v>-0.03166611385193917</v>
+        <v>-0.00024102406075299915</v>
       </c>
       <c r="K22">
-        <v>3.6665560287710455</v>
+        <v>3.569291240775846</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -867,13 +937,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-3.61967096177166e-7</v>
+        <v>-2.448289602036891e-7</v>
       </c>
       <c r="J23">
-        <v>-6.3935452331663115e-6</v>
+        <v>-2.1122073298971045e-7</v>
       </c>
       <c r="K23">
-        <v>1.9905395797376448</v>
+        <v>2.0446273817907348</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -902,13 +972,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.0001599558951234414</v>
+        <v>-2.40720527412969e-6</v>
       </c>
       <c r="J24">
-        <v>-0.0001287003705594839</v>
+        <v>-1.9996430169690206e-6</v>
       </c>
       <c r="K24">
-        <v>2.440494445088019</v>
+        <v>2.52831526204599</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>8.947155977465962e-8</v>
+        <v>-1.4761917650630022e-9</v>
       </c>
       <c r="J25">
-        <v>-1.097535490503784e-6</v>
+        <v>-1.5203848243686396e-8</v>
       </c>
       <c r="K25">
-        <v>1.6650627816199368</v>
+        <v>1.6813919153552614</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-2.505793557318932e-5</v>
+        <v>-3.2558494362268305e-7</v>
       </c>
       <c r="J26">
-        <v>-2.1083740797028566e-5</v>
+        <v>-2.751217857646763e-7</v>
       </c>
       <c r="K26">
-        <v>2.0555523759364207</v>
+        <v>2.0969133414434444</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-1.834542417985884e-6</v>
+        <v>-2.4997455264244678e-8</v>
       </c>
       <c r="J27">
-        <v>-1.31441944422948e-6</v>
+        <v>-1.8000429488889964e-8</v>
       </c>
       <c r="K27">
-        <v>1.4599323113693452</v>
+        <v>1.4957782778651763</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1042,13 +1112,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-1.5625194247435133e-6</v>
+        <v>-1.7779042410496155e-8</v>
       </c>
       <c r="J28">
-        <v>-2.1129064042268994e-6</v>
+        <v>-2.5636157106990134e-8</v>
       </c>
       <c r="K28">
-        <v>1.630183014993079</v>
+        <v>1.6510604148681631</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1077,13 +1147,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-9.455449761505957e-7</v>
+        <v>-1.2426530133215421e-8</v>
       </c>
       <c r="J29">
-        <v>-8.248769054617357e-7</v>
+        <v>-1.097446667264852e-8</v>
       </c>
       <c r="K29">
-        <v>1.3625010579046728</v>
+        <v>1.3956815049172908</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1112,13 +1182,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-5.530944917873012e-7</v>
+        <v>-7.456938141446535e-9</v>
       </c>
       <c r="J30">
-        <v>-5.411866265102695e-7</v>
+        <v>-7.385886154982109e-9</v>
       </c>
       <c r="K30">
-        <v>1.3035910390677206</v>
+        <v>1.3405358678595534</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1147,13 +1217,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-1.121307213644301e-6</v>
+        <v>-1.3570946077698945e-8</v>
       </c>
       <c r="J31">
-        <v>-1.0484769734307565e-6</v>
+        <v>-1.287024021270927e-8</v>
       </c>
       <c r="K31">
-        <v>1.4267215726785312</v>
+        <v>1.4461923001313202</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1182,13 +1252,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-6.504542610897691e-7</v>
+        <v>-8.266640872547543e-9</v>
       </c>
       <c r="J32">
-        <v>-5.718568923984392e-7</v>
+        <v>-7.394046776306677e-9</v>
       </c>
       <c r="K32">
-        <v>1.2890849202792798</v>
+        <v>1.3212866312599776</v>
       </c>
     </row>
   </sheetData>
